--- a/final/siruk-source-of-truth.xlsx
+++ b/final/siruk-source-of-truth.xlsx
@@ -39146,25 +39146,30 @@
         </is>
       </c>
       <c r="C881" s="3" t="n">
-        <v>410</v>
+        <v>500</v>
       </c>
       <c r="D881" s="3" t="n">
         <v>193</v>
       </c>
       <c r="E881" s="3" t="n">
-        <v>217</v>
+        <v>307</v>
       </c>
       <c r="F881" s="4" t="n">
-        <v>0.529</v>
+        <v>0.614</v>
       </c>
       <c r="G881" t="inlineStr">
         <is>
-          <t>user-approved 2026-10-15: 100 g loose, our bag rate +10%</t>
+          <t>zoovet.am per-kg loose price ÷ 10 (user 2026-10-15)</t>
         </is>
       </c>
       <c r="H881" t="inlineStr">
         <is>
           <t>https://siruk.am/product/trixie-cookie-bones/dp/2127/</t>
+        </is>
+      </c>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>https://zoovet.am/ru/sobaki/korma-i-lakomstva-1/lakomstva-2/sushenye-lakomstva-1/trixie-lakomstvo-kostochki-dlya-sobak-upakovka-1-3-kg-na-razves-1-kg</t>
         </is>
       </c>
       <c r="K881" t="inlineStr">
@@ -39229,25 +39234,30 @@
         </is>
       </c>
       <c r="C883" s="3" t="n">
-        <v>410</v>
+        <v>500</v>
       </c>
       <c r="D883" s="3" t="n">
         <v>193</v>
       </c>
       <c r="E883" s="3" t="n">
-        <v>217</v>
+        <v>307</v>
       </c>
       <c r="F883" s="4" t="n">
-        <v>0.529</v>
+        <v>0.614</v>
       </c>
       <c r="G883" t="inlineStr">
         <is>
-          <t>user-approved 2026-10-15: 100 g loose, our bag rate +10%</t>
+          <t>zoovet.am per-kg loose price ÷ 10 (user 2026-10-15)</t>
         </is>
       </c>
       <c r="H883" t="inlineStr">
         <is>
           <t>https://siruk.am/product/trixie-cookie-farmies/dp/2128/</t>
+        </is>
+      </c>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>https://zoovet.am/ru/sobaki/korma-i-lakomstva-1/lakomstva-2/sushenye-lakomstva-1/trixie-lakomstvo-mini-givotnye-dlya-sobak-upakovka-1-3-kg</t>
         </is>
       </c>
       <c r="K883" t="inlineStr">
@@ -39312,25 +39322,30 @@
         </is>
       </c>
       <c r="C885" s="3" t="n">
-        <v>370</v>
+        <v>520</v>
       </c>
       <c r="D885" s="3" t="n">
         <v>207</v>
       </c>
       <c r="E885" s="3" t="n">
-        <v>163</v>
+        <v>313</v>
       </c>
       <c r="F885" s="4" t="n">
-        <v>0.441</v>
+        <v>0.602</v>
       </c>
       <c r="G885" t="inlineStr">
         <is>
-          <t>user-approved 2026-10-15: 100 g loose, our bag rate +10%</t>
+          <t>zoovet.am per-kg loose price ÷ 10 (user 2026-10-15)</t>
         </is>
       </c>
       <c r="H885" t="inlineStr">
         <is>
           <t>https://siruk.am/product/trixie-cookie-giants-with-lamb/dp/2129/</t>
+        </is>
+      </c>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>https://zoovet.am/ru/sobaki/korma-i-lakomstva-1/lakomstva-2/myasnye-vyalenye-i-pechenye-lakomstva-1/trixie-lakomstvo-pechene-dlya-sobak-upakovka-1-25-kg-na-razves-1-kg</t>
         </is>
       </c>
       <c r="K885" t="inlineStr">
@@ -39395,25 +39410,30 @@
         </is>
       </c>
       <c r="C887" s="3" t="n">
-        <v>510</v>
+        <v>600</v>
       </c>
       <c r="D887" s="3" t="n">
         <v>221</v>
       </c>
       <c r="E887" s="3" t="n">
-        <v>289</v>
+        <v>379</v>
       </c>
       <c r="F887" s="4" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.632</v>
       </c>
       <c r="G887" t="inlineStr">
         <is>
-          <t>user-approved 2026-10-15: 100 g loose, our bag rate +10%</t>
+          <t>zoovet.am per-kg loose price ÷ 10 (user 2026-10-15)</t>
         </is>
       </c>
       <c r="H887" t="inlineStr">
         <is>
           <t>https://siruk.am/product/trixie-cookie-snack-loops/dp/2130/</t>
+        </is>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>https://zoovet.am/ru/sobaki/korma-i-lakomstva-1/lakomstva-2/myasnye-vyalenye-i-pechenye-lakomstva-1/trixie-lakomstvo-veganskie-kolechki-dlya-sobak-upakovka-1-3-kg-na-razves-1-kg</t>
         </is>
       </c>
       <c r="K887" t="inlineStr">
@@ -63389,25 +63409,30 @@
         </is>
       </c>
       <c r="C1433" s="3" t="n">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="D1433" s="3" t="n">
         <v>219</v>
       </c>
       <c r="E1433" s="3" t="n">
-        <v>481</v>
+        <v>431</v>
       </c>
       <c r="F1433" s="4" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.663</v>
       </c>
       <c r="G1433" t="inlineStr">
         <is>
-          <t>user-approved 2026-10-15: 100 g loose, our bag rate +10%</t>
+          <t>zoovet.am per-kg loose price ÷ 10 (user 2026-10-15)</t>
         </is>
       </c>
       <c r="H1433" t="inlineStr">
         <is>
           <t>https://siruk.am/product/trixie-soft-snack-bony-mix-xxl/dp/2126/</t>
+        </is>
+      </c>
+      <c r="I1433" t="inlineStr">
+        <is>
+          <t>https://zoovet.am/ru/sobaki/korma-i-lakomstva-1/lakomstva-2/sushenye-lakomstva-1/trixie-lakomstvo-bony-mix-mini-kostochki-s-govyadinoj-yagnenkom-tsyplenkom-i-ryboj-dlya-sobak-upakovka-1-8-kg</t>
         </is>
       </c>
       <c r="K1433" t="inlineStr">
@@ -73035,7 +73060,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>650</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -73062,7 +73087,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -73089,7 +73114,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -73116,7 +73141,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>520</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -73143,7 +73168,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>600</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">

--- a/final/siruk-source-of-truth.xlsx
+++ b/final/siruk-source-of-truth.xlsx
@@ -39146,20 +39146,20 @@
         </is>
       </c>
       <c r="C881" s="3" t="n">
-        <v>500</v>
+        <v>410</v>
       </c>
       <c r="D881" s="3" t="n">
         <v>193</v>
       </c>
       <c r="E881" s="3" t="n">
-        <v>307</v>
+        <v>217</v>
       </c>
       <c r="F881" s="4" t="n">
-        <v>0.614</v>
+        <v>0.529</v>
       </c>
       <c r="G881" t="inlineStr">
         <is>
-          <t>zoovet.am per-kg loose price ÷ 10 (user 2026-10-15)</t>
+          <t>user-approved 2026-10-15: 100 g loose, our bag rate +10% (no rival sells it by 100 g)</t>
         </is>
       </c>
       <c r="H881" t="inlineStr">
@@ -39167,11 +39167,7 @@
           <t>https://siruk.am/product/trixie-cookie-bones/dp/2127/</t>
         </is>
       </c>
-      <c r="I881" t="inlineStr">
-        <is>
-          <t>https://zoovet.am/ru/sobaki/korma-i-lakomstva-1/lakomstva-2/sushenye-lakomstva-1/trixie-lakomstvo-kostochki-dlya-sobak-upakovka-1-3-kg-na-razves-1-kg</t>
-        </is>
-      </c>
+      <c r="I881" t="inlineStr"/>
       <c r="K881" t="inlineStr">
         <is>
           <t>00108</t>
@@ -39234,20 +39230,20 @@
         </is>
       </c>
       <c r="C883" s="3" t="n">
-        <v>500</v>
+        <v>410</v>
       </c>
       <c r="D883" s="3" t="n">
         <v>193</v>
       </c>
       <c r="E883" s="3" t="n">
-        <v>307</v>
+        <v>217</v>
       </c>
       <c r="F883" s="4" t="n">
-        <v>0.614</v>
+        <v>0.529</v>
       </c>
       <c r="G883" t="inlineStr">
         <is>
-          <t>zoovet.am per-kg loose price ÷ 10 (user 2026-10-15)</t>
+          <t>user-approved 2026-10-15: 100 g loose, our bag rate +10% (no rival sells it by 100 g)</t>
         </is>
       </c>
       <c r="H883" t="inlineStr">
@@ -39255,11 +39251,7 @@
           <t>https://siruk.am/product/trixie-cookie-farmies/dp/2128/</t>
         </is>
       </c>
-      <c r="I883" t="inlineStr">
-        <is>
-          <t>https://zoovet.am/ru/sobaki/korma-i-lakomstva-1/lakomstva-2/sushenye-lakomstva-1/trixie-lakomstvo-mini-givotnye-dlya-sobak-upakovka-1-3-kg</t>
-        </is>
-      </c>
+      <c r="I883" t="inlineStr"/>
       <c r="K883" t="inlineStr">
         <is>
           <t>00109</t>
@@ -39322,20 +39314,20 @@
         </is>
       </c>
       <c r="C885" s="3" t="n">
-        <v>520</v>
+        <v>370</v>
       </c>
       <c r="D885" s="3" t="n">
         <v>207</v>
       </c>
       <c r="E885" s="3" t="n">
-        <v>313</v>
+        <v>163</v>
       </c>
       <c r="F885" s="4" t="n">
-        <v>0.602</v>
+        <v>0.441</v>
       </c>
       <c r="G885" t="inlineStr">
         <is>
-          <t>zoovet.am per-kg loose price ÷ 10 (user 2026-10-15)</t>
+          <t>user-approved 2026-10-15: 100 g loose, our bag rate +10% (no rival sells it by 100 g)</t>
         </is>
       </c>
       <c r="H885" t="inlineStr">
@@ -39343,11 +39335,7 @@
           <t>https://siruk.am/product/trixie-cookie-giants-with-lamb/dp/2129/</t>
         </is>
       </c>
-      <c r="I885" t="inlineStr">
-        <is>
-          <t>https://zoovet.am/ru/sobaki/korma-i-lakomstva-1/lakomstva-2/myasnye-vyalenye-i-pechenye-lakomstva-1/trixie-lakomstvo-pechene-dlya-sobak-upakovka-1-25-kg-na-razves-1-kg</t>
-        </is>
-      </c>
+      <c r="I885" t="inlineStr"/>
       <c r="K885" t="inlineStr">
         <is>
           <t>00110</t>
@@ -39410,20 +39398,20 @@
         </is>
       </c>
       <c r="C887" s="3" t="n">
-        <v>600</v>
+        <v>510</v>
       </c>
       <c r="D887" s="3" t="n">
         <v>221</v>
       </c>
       <c r="E887" s="3" t="n">
-        <v>379</v>
+        <v>289</v>
       </c>
       <c r="F887" s="4" t="n">
-        <v>0.632</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G887" t="inlineStr">
         <is>
-          <t>zoovet.am per-kg loose price ÷ 10 (user 2026-10-15)</t>
+          <t>user-approved 2026-10-15: 100 g loose, our bag rate +10% (no rival sells it by 100 g)</t>
         </is>
       </c>
       <c r="H887" t="inlineStr">
@@ -39431,11 +39419,7 @@
           <t>https://siruk.am/product/trixie-cookie-snack-loops/dp/2130/</t>
         </is>
       </c>
-      <c r="I887" t="inlineStr">
-        <is>
-          <t>https://zoovet.am/ru/sobaki/korma-i-lakomstva-1/lakomstva-2/myasnye-vyalenye-i-pechenye-lakomstva-1/trixie-lakomstvo-veganskie-kolechki-dlya-sobak-upakovka-1-3-kg-na-razves-1-kg</t>
-        </is>
-      </c>
+      <c r="I887" t="inlineStr"/>
       <c r="K887" t="inlineStr">
         <is>
           <t>00111</t>
@@ -63409,20 +63393,20 @@
         </is>
       </c>
       <c r="C1433" s="3" t="n">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="D1433" s="3" t="n">
         <v>219</v>
       </c>
       <c r="E1433" s="3" t="n">
-        <v>431</v>
+        <v>481</v>
       </c>
       <c r="F1433" s="4" t="n">
-        <v>0.663</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="G1433" t="inlineStr">
         <is>
-          <t>zoovet.am per-kg loose price ÷ 10 (user 2026-10-15)</t>
+          <t>user-approved 2026-10-15: 100 g loose, our bag rate +10% (no rival sells it by 100 g)</t>
         </is>
       </c>
       <c r="H1433" t="inlineStr">
@@ -63430,11 +63414,7 @@
           <t>https://siruk.am/product/trixie-soft-snack-bony-mix-xxl/dp/2126/</t>
         </is>
       </c>
-      <c r="I1433" t="inlineStr">
-        <is>
-          <t>https://zoovet.am/ru/sobaki/korma-i-lakomstva-1/lakomstva-2/sushenye-lakomstva-1/trixie-lakomstvo-bony-mix-mini-kostochki-s-govyadinoj-yagnenkom-tsyplenkom-i-ryboj-dlya-sobak-upakovka-1-8-kg</t>
-        </is>
-      </c>
+      <c r="I1433" t="inlineStr"/>
       <c r="K1433" t="inlineStr">
         <is>
           <t>00107</t>
@@ -73060,7 +73040,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>700</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -73087,7 +73067,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>410</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -73114,7 +73094,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>410</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -73141,7 +73121,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>370</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -73168,7 +73148,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>510</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">

--- a/final/siruk-source-of-truth.xlsx
+++ b/final/siruk-source-of-truth.xlsx
@@ -39146,20 +39146,20 @@
         </is>
       </c>
       <c r="C881" s="3" t="n">
-        <v>410</v>
+        <v>550</v>
       </c>
       <c r="D881" s="3" t="n">
         <v>193</v>
       </c>
       <c r="E881" s="3" t="n">
-        <v>217</v>
+        <v>357</v>
       </c>
       <c r="F881" s="4" t="n">
-        <v>0.529</v>
+        <v>0.649</v>
       </c>
       <c r="G881" t="inlineStr">
         <is>
-          <t>user-approved 2026-10-15: 100 g loose, our bag rate +10% (no rival sells it by 100 g)</t>
+          <t>user-approved 2026-10-15: 100 g loose, zoovet.am per-kg loose price +10% (no rival sells it by 100 g)</t>
         </is>
       </c>
       <c r="H881" t="inlineStr">
@@ -39230,20 +39230,20 @@
         </is>
       </c>
       <c r="C883" s="3" t="n">
-        <v>410</v>
+        <v>550</v>
       </c>
       <c r="D883" s="3" t="n">
         <v>193</v>
       </c>
       <c r="E883" s="3" t="n">
-        <v>217</v>
+        <v>357</v>
       </c>
       <c r="F883" s="4" t="n">
-        <v>0.529</v>
+        <v>0.649</v>
       </c>
       <c r="G883" t="inlineStr">
         <is>
-          <t>user-approved 2026-10-15: 100 g loose, our bag rate +10% (no rival sells it by 100 g)</t>
+          <t>user-approved 2026-10-15: 100 g loose, zoovet.am per-kg loose price +10% (no rival sells it by 100 g)</t>
         </is>
       </c>
       <c r="H883" t="inlineStr">
@@ -39314,20 +39314,20 @@
         </is>
       </c>
       <c r="C885" s="3" t="n">
-        <v>370</v>
+        <v>570</v>
       </c>
       <c r="D885" s="3" t="n">
         <v>207</v>
       </c>
       <c r="E885" s="3" t="n">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="F885" s="4" t="n">
-        <v>0.441</v>
+        <v>0.637</v>
       </c>
       <c r="G885" t="inlineStr">
         <is>
-          <t>user-approved 2026-10-15: 100 g loose, our bag rate +10% (no rival sells it by 100 g)</t>
+          <t>user-approved 2026-10-15: 100 g loose, zoovet.am per-kg loose price +10% (no rival sells it by 100 g)</t>
         </is>
       </c>
       <c r="H885" t="inlineStr">
@@ -39398,20 +39398,20 @@
         </is>
       </c>
       <c r="C887" s="3" t="n">
-        <v>510</v>
+        <v>660</v>
       </c>
       <c r="D887" s="3" t="n">
         <v>221</v>
       </c>
       <c r="E887" s="3" t="n">
-        <v>289</v>
+        <v>439</v>
       </c>
       <c r="F887" s="4" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.665</v>
       </c>
       <c r="G887" t="inlineStr">
         <is>
-          <t>user-approved 2026-10-15: 100 g loose, our bag rate +10% (no rival sells it by 100 g)</t>
+          <t>user-approved 2026-10-15: 100 g loose, zoovet.am per-kg loose price +10% (no rival sells it by 100 g)</t>
         </is>
       </c>
       <c r="H887" t="inlineStr">
@@ -73067,7 +73067,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>550</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -73094,7 +73094,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>550</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -73121,7 +73121,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>570</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -73148,7 +73148,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>660</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
